--- a/schools-presentations/A Gymnasiou/kahoot/A5.3 Μ1 - Κίνδυνοι στο Διαδίκτυο.xlsx
+++ b/schools-presentations/A Gymnasiou/kahoot/A5.3 Μ1 - Κίνδυνοι στο Διαδίκτυο.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kahoot Quiz" sheetId="1" r:id="R767ad7d844964f09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kahoot Quiz" sheetId="1" r:id="Rf0d0cbf8bc204434"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,7 +55,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF4CC"/>
+        <x:fgColor rgb="FFFFF1C7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -340,30 +340,30 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="31" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="31" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="31" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="31" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>Question - max 95 characters</x:v>
+        <x:v>Question - max 120 characters</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>Answer 1 - max 60 characters</x:v>
+        <x:v>Answer 1 - max 75 characters</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>Answer 2 - max 60 characters</x:v>
+        <x:v>Answer 2 - max 75 characters</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>Answer 3 - max 60 characters</x:v>
+        <x:v>Answer 3 - max 75 characters</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>Answer 4 - max 60 characters</x:v>
+        <x:v>Answer 4 - max 75 characters</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
         <x:v>Time limit (sec)</x:v>
@@ -372,67 +372,67 @@
         <x:v>Correct answer(s)</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="58" customHeight="1">
+    <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" s="11" t="str">
         <x:v>Τι είναι ένα κακόβουλο πρόγραμμα;</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Πρόγραμμα που μπορεί να βλάψει τον υπολογιστή</x:v>
+        <x:v>Εφαρμογή που οργανώνει τα αρχεία μας</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>Πρόγραμμα δημιουργίας παρουσιάσεων</x:v>
+        <x:v>Λογισμικό που μπορεί να βλάψει συσκευή ή δεδομένα</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>Φίλτρο ανεπιθύμητων μηνυμάτων</x:v>
+        <x:v>Πρόγραμμα που ελέγχει μόνο την ταχύτητα δικτύου</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>Μηχανή αναζήτησης</x:v>
+        <x:v>Εργαλείο που δημιουργεί αντίγραφα ασφαλείας</x:v>
       </x:c>
       <x:c r="F2" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G2" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="58" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" s="11" t="str">
-        <x:v>Πώς φτάνουν συχνά οι ιοί στον υπολογιστή;</x:v>
+        <x:v>Πώς μπορεί να φτάσει κακόβουλο λογισμικό σε έναν υπολογιστή;</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>Μέσα από ύποπτα επισυναπτόμενα αρχεία</x:v>
+        <x:v>Μόνο μέσω νόμιμης ενημέρωσης</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>Μέσα από το πληκτρολόγιο</x:v>
+        <x:v>Μόνο με σύνδεση εκτυπωτή</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>Μέσα από την οθόνη</x:v>
+        <x:v>Μόνο όταν ανοίγει το πρόγραμμα e-mail</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>Μέσα από νόμιμα αντίγραφα ασφαλείας</x:v>
+        <x:v>Μέσω ύποπτου συνδέσμου ή συνημμένου</x:v>
       </x:c>
       <x:c r="F3" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G3" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" s="11" t="str">
-        <x:v>Ποιος είναι ο ρόλος ενός antivirus;</x:v>
+        <x:v>Ποιος είναι ο βασικός ρόλος του antivirus;</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Εντοπίζει, απομονώνει ή διαγράφει κακόβουλα αρχεία</x:v>
+        <x:v>Εντοπίζει και αντιμετωπίζει γνωστές απειλές</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>Δημιουργεί λογαριασμούς e-mail</x:v>
+        <x:v>Δημιουργεί ισχυρούς κωδικούς για κάθε ιστοσελίδα</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>Αποθηκεύει σελιδοδείκτες</x:v>
+        <x:v>Αποκλείει όλα τα μηνύματα ηλεκτρονικού ταχυδρομείου</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>Απαντά αυτόματα σε όλα τα μηνύματα</x:v>
+        <x:v>Κρύβει τη διεύθυνση e-mail από τις επαφές μας</x:v>
       </x:c>
       <x:c r="F4" s="14" t="n">
         <x:v>30</x:v>
@@ -441,90 +441,90 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="58" customHeight="1">
+    <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" s="11" t="str">
-        <x:v>Τι είναι το Spam;</x:v>
+        <x:v>Τι ονομάζουμε Spam;</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Μαζικά ανεπιθύμητα μηνύματα</x:v>
+        <x:v>Μήνυμα που αποθηκεύσαμε ως Πρόχειρο</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>Μήνυμα από γνωστό φίλο</x:v>
+        <x:v>Απάντηση που στείλαμε κατά λάθος σε όλους</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>Αντίγραφο ασφαλείας</x:v>
+        <x:v>Μαζικό ανεπιθύμητο μήνυμα</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>Ενημέρωση του antivirus</x:v>
+        <x:v>Ενημέρωση ασφαλείας από το λειτουργικό σύστημα</x:v>
       </x:c>
       <x:c r="F5" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="58" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" s="11" t="str">
-        <x:v>Πώς περιορίζουμε τα ανεπιθύμητα μηνύματα;</x:v>
+        <x:v>Ποια ενέργεια βοηθά να περιοριστεί το Spam;</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Ενεργοποιούμε φίλτρα ανεπιθύμητης αλληλογραφίας</x:v>
+        <x:v>Απάντηση με αίτημα διαγραφής σε κάθε ύποπτο μήνυμα</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Απαντούμε σε κάθε μήνυμα</x:v>
+        <x:v>Χρήση φίλτρων ανεπιθύμητης αλληλογραφίας</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>Δίνουμε παντού τη διεύθυνσή μας</x:v>
+        <x:v>Δημοσίευση της διεύθυνσης e-mail σε δημόσιες σελίδες</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>Ανοίγουμε όλα τα συνημμένα</x:v>
+        <x:v>Άνοιγμα των μηνυμάτων για έλεγχο του αποστολέα</x:v>
       </x:c>
       <x:c r="F6" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G6" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="58" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" s="11" t="str">
         <x:v>Τι είναι το Phishing;</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Παραπλάνηση για κλοπή προσωπικών στοιχείων</x:v>
+        <x:v>Ενημέρωση του antivirus από επίσημη πηγή</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>Πρόγραμμα καταπολέμησης ιών</x:v>
+        <x:v>Αποθήκευση αρχείων σε δεύτερο μέσο</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>Μαζική αποστολή διαφημίσεων</x:v>
+        <x:v>Φιλτράρισμα ανεπιθύμητων διαφημίσεων</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>Δημιουργία αντιγράφων ασφαλείας</x:v>
+        <x:v>Παραπλάνηση για υποκλοπή προσωπικών στοιχείων</x:v>
       </x:c>
       <x:c r="F7" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G7" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" s="11" t="str">
-        <x:v>Ποιο στοιχείο δεν πρέπει να στέλνουμε μέσω e-mail;</x:v>
+        <x:v>Ποιο στοιχείο δεν πρέπει να αποκαλύπτουμε μέσω e-mail;</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Τον προσωπικό μας κωδικό πρόσβασης</x:v>
+        <x:v>Τον προσωπικό κωδικό πρόσβασης</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>Το όνομα ενός μαθήματος</x:v>
+        <x:v>Τον τίτλο μιας σχολικής εργασίας</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>Μια γενική ευχή</x:v>
+        <x:v>Μια γενική ερώτηση για το μάθημα</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>Τον τίτλο ενός βιβλίου</x:v>
+        <x:v>Το όνομα ενός δημόσιου οργανισμού</x:v>
       </x:c>
       <x:c r="F8" s="14" t="n">
         <x:v>20</x:v>
@@ -533,67 +533,67 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="58" customHeight="1">
+    <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" s="11" t="str">
-        <x:v>Ποια ενέργεια βοηθά στην προστασία από νέους ιούς;</x:v>
+        <x:v>Τι αυξάνει την προστασία από νέες απειλές;</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>Η συχνή ενημέρωση του antivirus</x:v>
+        <x:v>Η απενεργοποίηση των ενημερώσεων</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Η απενεργοποίηση όλων των ενημερώσεων</x:v>
+        <x:v>Η χρήση του ίδιου κωδικού παντού</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>Η απάντηση σε spam</x:v>
+        <x:v>Η τακτική ενημέρωση λειτουργικού και antivirus</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>Η κοινοποίηση του κωδικού μας</x:v>
+        <x:v>Η μεταφορά ύποπτων μηνυμάτων στα Πρόχειρα</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="58" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" s="13" t="str">
-        <x:v>Άγνωστος στέλνει αρχείο «photo.jpg.vbs». Τι είναι ασφαλέστερο;</x:v>
+        <x:v>Άγνωστος στέλνει το αρχείο «photo.jpg.vbs». Ποια είναι η ασφαλέστερη αντίδραση;</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Το ανοίγουμε επειδή γράφει photo</x:v>
+        <x:v>Άνοιγμα, επειδή περιέχει τη λέξη photo</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>Το προωθούμε σε φίλο</x:v>
+        <x:v>Μετονομασία σε photo.jpg και μετά άνοιγμα</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
-        <x:v>Δεν το ανοίγουμε και το αναφέρουμε</x:v>
+        <x:v>Προώθηση σε φίλο για να το δοκιμάσει</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
-        <x:v>Αλλάζουμε μόνο το όνομα του αρχείου</x:v>
+        <x:v>Δεν το ανοίγουμε, το διαγράφουμε ή το αναφέρουμε</x:v>
       </x:c>
       <x:c r="F10" s="15" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="G10" s="15" t="str">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="62" customHeight="1">
       <x:c r="A11" s="13" t="str">
-        <x:v>Μήνυμα τράπεζας ζητά PIN «άμεσα» μέσω συνδέσμου. Τι κάνουμε;</x:v>
+        <x:v>Μήνυμα “τράπεζας” ζητά PIN άμεσα από σύνδεσμο. Τι κάνουμε πρώτα;</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>Δίνουμε το PIN για να μη κλείσει η κάρτα</x:v>
+        <x:v>Απαντούμε ζητώντας να επιβεβαιώσουν το όνομά μας</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
-        <x:v>Δεν πατάμε· επικοινωνούμε από επίσημο κανάλι</x:v>
+        <x:v>Δεν πατάμε και επικοινωνούμε από το επίσημο κανάλι της τράπεζας</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>Απαντούμε ζητώντας περισσότερες πληροφορίες</x:v>
+        <x:v>Πατάμε τον σύνδεσμο, αλλά δεν πληκτρολογούμε το PIN</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>Προωθούμε το μήνυμα στους φίλους μας</x:v>
+        <x:v>Προωθούμε το μήνυμα σε συγγενή για επιβεβαίωση</x:v>
       </x:c>
       <x:c r="F11" s="15" t="n">
         <x:v>60</x:v>
